--- a/results/momentum_strong_2026-10-06.xlsx
+++ b/results/momentum_strong_2026-10-06.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D238"/>
+  <dimension ref="A1:D231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,11 +449,7 @@
           <t>ABLV</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>BZFD</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>AAON</t>
@@ -463,7 +459,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AIIA</t>
+          <t>BOT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -471,456 +467,404 @@
           <t>ABSI</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>FUFU</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AMBA</t>
+          <t>ATOM</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CHSCO</t>
+          <t>CURX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ACU</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>GNLN</t>
-        </is>
-      </c>
+          <t>ABXL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ATII</t>
+          <t>AZUL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CRVO</t>
+          <t>DLXY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADMA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>HTLM</t>
-        </is>
-      </c>
+          <t>ACLS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AVO</t>
+          <t>BTTC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ELLA</t>
+          <t>DUKRW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ADPT</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>RGC</t>
-        </is>
-      </c>
+          <t>ADI</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CRUS</t>
+          <t>CRD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>FRSH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AEHL</t>
+          <t>ADMA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>CRNT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AEIS</t>
+          <t>ADPT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>HWKN</t>
+          <t>CRWV</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GSRF</t>
+          <t>KBSX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AGEN</t>
+          <t>AEHL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ICHR</t>
+          <t>DMRC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>INAB</t>
+          <t>MACI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AIIR</t>
+          <t>AEHR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>INDV</t>
+          <t>DUOT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KFII</t>
+          <t>MDAI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>AEIS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>IQMX</t>
+          <t>EMPD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NAUT</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ALMR</t>
+          <t>AFRI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IRMD</t>
+          <t>EVCM</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NSLRL</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ALNT</t>
+          <t>AHG</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>HBANL</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NTWK</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AMPH</t>
+          <t>AIB</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MAZE</t>
+          <t>HYPR</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>OPTX</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>AIIR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MDLN</t>
+          <t>INEO</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>OXLCM</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MKSI</t>
+          <t>IQMX</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>PDSB</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ANGI</t>
+          <t>ALLT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NEON</t>
+          <t>ITRN</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>PMTR</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AOUT</t>
+          <t>ALNT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PWRL</t>
+          <t>MAZE</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>PTC</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ARAY</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SLMT</t>
+          <t>MIND</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>PXS</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ARW</t>
+          <t>AMBR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TLN</t>
+          <t>NMAD</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>RELL</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ASPS</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VERU</t>
+          <t>NTRSO</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>RXRX</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ASST</t>
+          <t>AMPH</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ZSQR</t>
+          <t>POWL</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>SDEV</t>
-        </is>
-      </c>
+      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
+          <t>AMPL</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>QUIK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>AMRX</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>RYAAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ANDG</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SNWV</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ASST</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>STRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>ATKR</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>SOTK</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>ATLCL</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>SXTP</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>AUUD</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>THEO</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>AVPT</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>WCCB</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>AZTA</t>
-        </is>
-      </c>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TLN</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BCML</t>
+          <t>AVAT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ZSQR</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BCTX</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -930,7 +874,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BKHA</t>
+          <t>AVX</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -940,7 +884,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BLRK</t>
+          <t>AXTI</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -950,7 +894,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BNC</t>
+          <t>BATRA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -960,7 +904,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BPRE</t>
+          <t>BBCP</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -970,7 +914,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>BCAL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -980,7 +924,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BTBD</t>
+          <t>BELFB</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -990,7 +934,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BTTC</t>
+          <t>BMNR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -1000,7 +944,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>BNR</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -1010,7 +954,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BZUN</t>
+          <t>BOW</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -1020,7 +964,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CAMT</t>
+          <t>BPRE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -1030,7 +974,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>BSVN</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -1040,7 +984,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>BTBD</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -1050,7 +994,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CELU</t>
+          <t>BZUN</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -1060,7 +1004,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>CBAT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -1070,7 +1014,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CFFI</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1080,7 +1024,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CHAD</t>
+          <t>CDNS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1090,7 +1034,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CHEF</t>
+          <t>CELU</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1100,7 +1044,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CHSCL</t>
+          <t>CEVA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1110,7 +1054,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CLMB</t>
+          <t>CFFI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1120,7 +1064,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>COHU</t>
+          <t>CGNT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1130,7 +1074,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CORT</t>
+          <t>CGNX</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1140,7 +1084,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>COSM</t>
+          <t>CHAD</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1150,7 +1094,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>CHSCL</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1160,7 +1104,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>CLMB</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1170,7 +1114,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CRSR</t>
+          <t>CNXN</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1180,7 +1124,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1190,7 +1134,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1200,7 +1144,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CSTL</t>
+          <t>CRAI</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1210,7 +1154,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CTKB</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1220,7 +1164,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1230,7 +1174,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CWBC</t>
+          <t>CTKB</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1240,7 +1184,7 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CYRX</t>
+          <t>CVCO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1250,7 +1194,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>CVLT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1260,7 +1204,7 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DMAC</t>
+          <t>CWBC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1270,7 +1214,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DMRC</t>
+          <t>DDI</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1280,7 +1224,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DOCU</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1290,7 +1234,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>DIOD</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1300,7 +1244,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>DSGR</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1310,7 +1254,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DTST</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1320,7 +1264,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EEIQ</t>
+          <t>DXPE</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1330,7 +1274,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>EGBN</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1340,7 +1284,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FBLA</t>
+          <t>EGHT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1350,7 +1294,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>ELMT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1360,7 +1304,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>EMBC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1370,7 +1314,7 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FIRY</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1380,7 +1324,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FLGT</t>
+          <t>ENTG</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1390,7 +1334,7 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FNRN</t>
+          <t>EUDA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1400,7 +1344,7 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FORM</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1410,7 +1354,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FRHC</t>
+          <t>FBLA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1420,7 +1364,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>FEIM</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1430,7 +1374,7 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1440,7 +1384,7 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>FIRY</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1450,7 +1394,7 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1460,7 +1404,7 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>FMAO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1470,7 +1414,7 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GSAT</t>
+          <t>FOSL</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1480,7 +1424,7 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GTLB</t>
+          <t>FPS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1490,7 +1434,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>HBIO</t>
+          <t>FRHC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1500,7 +1444,7 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>HIMX</t>
+          <t>FROG</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1510,7 +1454,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>FSBW</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1520,7 +1464,7 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>HSTM</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1530,7 +1474,7 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>HTFL</t>
+          <t>FTRE</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1540,7 +1484,7 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>IBRX</t>
+          <t>FWDI</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1550,7 +1494,7 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IDAI</t>
+          <t>GCT</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -1560,7 +1504,7 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>GRDX</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -1570,7 +1514,7 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>GTLB</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -1580,7 +1524,7 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>IMPPP</t>
+          <t>HBIO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -1590,7 +1534,7 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>INCR</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -1600,7 +1544,7 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>INKT</t>
+          <t>HQI</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -1610,7 +1554,7 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>HQWWW</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -1620,7 +1564,7 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>HWKN</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -1630,7 +1574,7 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>IPGP</t>
+          <t>IESC</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -1640,7 +1584,7 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>INKT</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -1650,7 +1594,7 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>JAKK</t>
+          <t>IOSP</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -1660,7 +1604,7 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>IRDM</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -1690,7 +1634,7 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>KAZR</t>
+          <t>KFII</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -1700,7 +1644,7 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>KCHV</t>
+          <t>KMRK</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -1710,7 +1654,7 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>KFFB</t>
+          <t>KMTS</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -1720,7 +1664,7 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>KMTS</t>
+          <t>KOD</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -1730,7 +1674,7 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>KOD</t>
+          <t>KOPN</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -1740,7 +1684,7 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>KOSS</t>
+          <t>LCUT</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -1750,7 +1694,7 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>KRNT</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -1760,7 +1704,7 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>LEDS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -1770,7 +1714,7 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>LAFA</t>
+          <t>LGND</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -1780,7 +1724,7 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>LIND</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -1790,7 +1734,7 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -1800,7 +1744,7 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>LGND</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -1810,7 +1754,7 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LIND</t>
+          <t>LITS</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -1820,7 +1764,7 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>LKFT</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -1830,7 +1774,7 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>LOPE</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -1840,7 +1784,7 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>LKFT</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -1870,7 +1814,7 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>MANE</t>
+          <t>LTRX</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -1880,7 +1824,7 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>MATH</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -1890,7 +1834,7 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>MBINM</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -1900,7 +1844,7 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>MCHP</t>
+          <t>MCHPP</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -1910,7 +1854,7 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>MGNI</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -1920,7 +1864,7 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MKTW</t>
+          <t>MGRC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -1930,7 +1874,7 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MLAB</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -1940,7 +1884,7 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>MNTK</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -1950,7 +1894,7 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>MSGY</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -1960,7 +1904,7 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -1970,7 +1914,7 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>MRVI</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -1980,7 +1924,7 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>MTSI</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -1990,7 +1934,7 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>MSGM</t>
+          <t>MXL</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -2000,7 +1944,7 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>NATH</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -2010,7 +1954,7 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>MTSI</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -2020,7 +1964,7 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>NCPL</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -2030,7 +1974,7 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>MXL</t>
+          <t>NDSN</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -2040,7 +1984,7 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>NAKA</t>
+          <t>NICE</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -2050,7 +1994,7 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>NATH</t>
+          <t>NKSH</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -2060,7 +2004,7 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>NOVT</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -2070,7 +2014,7 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>NCPL</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -2080,7 +2024,7 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>NDRA</t>
+          <t>NTCT</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -2090,7 +2034,7 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>NTNX</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -2100,7 +2044,7 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>NHPBP</t>
+          <t>NTRP</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -2110,7 +2054,7 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>NTCT</t>
+          <t>NTSK</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -2120,7 +2064,7 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -2130,7 +2074,7 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -2140,7 +2084,7 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NTRP</t>
+          <t>NVEC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -2150,7 +2094,7 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -2160,7 +2104,7 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>NUTX</t>
+          <t>OCC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -2170,7 +2114,7 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>NVAX</t>
+          <t>OESX</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -2180,7 +2124,7 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -2190,7 +2134,7 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>NVEC</t>
+          <t>ONC</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -2200,7 +2144,7 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>OCTV</t>
+          <t>OPRT</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -2210,7 +2154,7 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ODD</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -2220,7 +2164,7 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>OPTX</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -2230,7 +2174,7 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>OLLI</t>
+          <t>OSPN</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -2240,7 +2184,7 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>OTAI</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -2250,7 +2194,7 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>OPRT</t>
+          <t>OUST</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -2260,7 +2204,7 @@
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="inlineStr">
         <is>
-          <t>OPRX</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -2270,7 +2214,7 @@
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>OSPN</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -2280,7 +2224,7 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>OSUR</t>
+          <t>PDFS</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -2290,7 +2234,7 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>OTAI</t>
+          <t>PKOH</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -2300,7 +2244,7 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>OXLCZ</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -2310,7 +2254,7 @@
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>PLXS</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -2320,7 +2264,7 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PACB</t>
+          <t>PMVP</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -2330,7 +2274,7 @@
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>PPIH</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -2340,7 +2284,7 @@
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PAYO</t>
+          <t>PRCH</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -2350,7 +2294,7 @@
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>PS</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -2360,7 +2304,7 @@
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PDFS</t>
+          <t>PSIG</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -2370,7 +2314,7 @@
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PENG</t>
+          <t>PSIX</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -2380,7 +2324,7 @@
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PKOH</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -2390,7 +2334,7 @@
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PLUN</t>
+          <t>PUBM</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -2400,7 +2344,7 @@
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PLXS</t>
+          <t>PWP</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -2410,7 +2354,7 @@
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>PXS</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -2420,7 +2364,7 @@
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PPLI</t>
+          <t>QMCO</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -2430,7 +2374,7 @@
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>QSI</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -2440,7 +2384,7 @@
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>RBKB</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -2450,7 +2394,7 @@
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="inlineStr">
         <is>
-          <t>QLYS</t>
+          <t>RCBC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -2460,7 +2404,7 @@
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="inlineStr">
         <is>
-          <t>QNBC</t>
+          <t>RDVT</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -2470,7 +2414,7 @@
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="inlineStr">
         <is>
-          <t>QSEA</t>
+          <t>RDWR</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -2480,7 +2424,7 @@
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="inlineStr">
         <is>
-          <t>QTRX</t>
+          <t>RFAI</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -2490,7 +2434,7 @@
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -2500,7 +2444,7 @@
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="inlineStr">
         <is>
-          <t>RCMT</t>
+          <t>RMBS</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -2510,7 +2454,7 @@
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="inlineStr">
         <is>
-          <t>RDWR</t>
+          <t>RVMD</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -2520,7 +2464,7 @@
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="inlineStr">
         <is>
-          <t>REFR</t>
+          <t>RWAYL</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -2530,7 +2474,7 @@
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="inlineStr">
         <is>
-          <t>RFAI</t>
+          <t>SBC</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -2540,7 +2484,7 @@
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="inlineStr">
         <is>
-          <t>RILYG</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -2550,7 +2494,7 @@
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="inlineStr">
         <is>
-          <t>RUSHB</t>
+          <t>SCSC</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -2560,7 +2504,7 @@
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="inlineStr">
         <is>
-          <t>RVSB</t>
+          <t>SDGR</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -2570,7 +2514,7 @@
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="inlineStr">
         <is>
-          <t>SAMG</t>
+          <t>SGC</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -2580,7 +2524,7 @@
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SANM</t>
+          <t>SHLS</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -2590,7 +2534,7 @@
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SAX</t>
+          <t>SHMD</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -2600,7 +2544,7 @@
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -2610,7 +2554,7 @@
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="inlineStr">
         <is>
-          <t>SCSC</t>
+          <t>SILC</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -2620,7 +2564,7 @@
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="inlineStr">
         <is>
-          <t>SCYX</t>
+          <t>SIMO</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -2630,7 +2574,7 @@
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr">
         <is>
-          <t>SDGR</t>
+          <t>SITM</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -2640,7 +2584,7 @@
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr">
         <is>
-          <t>SEER</t>
+          <t>SKYA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -2650,7 +2594,7 @@
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="inlineStr">
         <is>
-          <t>SGC</t>
+          <t>SMMT</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -2660,7 +2604,7 @@
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -2670,7 +2614,7 @@
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="inlineStr">
         <is>
-          <t>SIGA</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -2680,7 +2624,7 @@
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="inlineStr">
         <is>
-          <t>SILC</t>
+          <t>SOTK</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -2690,7 +2634,7 @@
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="inlineStr">
         <is>
-          <t>SIMO</t>
+          <t>SPCX</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -2700,7 +2644,7 @@
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SINT</t>
+          <t>SPOK</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -2710,7 +2654,7 @@
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="inlineStr">
         <is>
-          <t>SITM</t>
+          <t>SSTI</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -2720,7 +2664,7 @@
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="inlineStr">
         <is>
-          <t>SKHY</t>
+          <t>STRC</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -2730,7 +2674,7 @@
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="inlineStr">
         <is>
-          <t>SLAB</t>
+          <t>STRD</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -2740,7 +2684,7 @@
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="inlineStr">
         <is>
-          <t>SLGL</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -2750,7 +2694,7 @@
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>SUIG</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -2760,7 +2704,7 @@
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>SUJA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -2770,7 +2714,7 @@
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="inlineStr">
         <is>
-          <t>SRZN</t>
+          <t>SUNB</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -2780,7 +2724,7 @@
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="inlineStr">
         <is>
-          <t>SSYS</t>
+          <t>SVCO</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -2790,7 +2734,7 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>STRC</t>
+          <t>TAOX</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -2800,7 +2744,7 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>STRD</t>
+          <t>TEM</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -2810,7 +2754,7 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>STRF</t>
+          <t>TENB</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -2820,7 +2764,7 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>TITN</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -2830,7 +2774,7 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>SUIG</t>
+          <t>TLSA</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -2840,7 +2784,7 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>SUNB</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -2850,7 +2794,7 @@
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="inlineStr">
         <is>
-          <t>SVIA</t>
+          <t>TRNI</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -2860,7 +2804,7 @@
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="inlineStr">
         <is>
-          <t>SVRN</t>
+          <t>TRNS</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -2870,7 +2814,7 @@
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="inlineStr">
         <is>
-          <t>SWBI</t>
+          <t>USDEW</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -2880,7 +2824,7 @@
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="inlineStr">
         <is>
-          <t>SWKHL</t>
+          <t>VAI</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -2890,7 +2834,7 @@
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="inlineStr">
         <is>
-          <t>TAOX</t>
+          <t>WCCB</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -2900,7 +2844,7 @@
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>WLTH</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -2910,7 +2854,7 @@
       <c r="A228" t="inlineStr"/>
       <c r="B228" t="inlineStr">
         <is>
-          <t>TENB</t>
+          <t>XFLH</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -2920,7 +2864,7 @@
       <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr">
         <is>
-          <t>TONT</t>
+          <t>XMTR</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -2930,7 +2874,7 @@
       <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>XRPN</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -2940,81 +2884,11 @@
       <c r="A231" t="inlineStr"/>
       <c r="B231" t="inlineStr">
         <is>
-          <t>TRNS</t>
+          <t>XXI</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr"/>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr"/>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>TWAV</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr"/>
-      <c r="D232" t="inlineStr"/>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr"/>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>VALU</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr"/>
-      <c r="D233" t="inlineStr"/>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr"/>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>VIR</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr"/>
-      <c r="D234" t="inlineStr"/>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr"/>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>WLTH</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr"/>
-      <c r="D235" t="inlineStr"/>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr"/>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>XFLH</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr"/>
-      <c r="D236" t="inlineStr"/>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr"/>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>XMTR</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr"/>
-      <c r="D237" t="inlineStr"/>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr"/>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>XRPNU</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr"/>
-      <c r="D238" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
